--- a/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>1000</t>
+  </si>
+  <si>
+    <t>300</t>
   </si>
   <si>
     <t>Bear</t>
@@ -706,180 +709,180 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="5" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="6" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="7" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="7" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="8" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="34" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1205,9 +1208,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AK27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -1240,8 +1243,8 @@
     <col min="37" max="37" width="2.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:29">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1285,8 +1288,8 @@
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:29">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1330,8 +1333,8 @@
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:29">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1"/>
@@ -1367,8 +1370,8 @@
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:29">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1434,7 +1437,7 @@
       </c>
       <c r="AC4" s="6"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:29">
       <c r="B5" s="7">
         <v>1001</v>
       </c>
@@ -1520,7 +1523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:29">
       <c r="B6" s="7">
         <v>1002</v>
       </c>
@@ -1606,7 +1609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:29">
       <c r="B7" s="7">
         <v>1003</v>
       </c>
@@ -1671,7 +1674,7 @@
         <v>1001</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="X7" s="7">
         <v>10041</v>
@@ -1692,7 +1695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:29">
       <c r="B8" s="7">
         <v>1004</v>
       </c>
@@ -1700,16 +1703,16 @@
         <v>44</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H8" s="9">
         <v>10001</v>
@@ -1778,24 +1781,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:29">
       <c r="B9" s="7">
         <v>1005</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>42</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H9" s="9">
         <v>10001</v>
@@ -1859,7 +1862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:29">
       <c r="B10" s="13">
         <v>1006</v>
       </c>
@@ -1867,11 +1870,11 @@
         <v>32</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>36</v>
@@ -1880,7 +1883,7 @@
         <v>10001</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J10" s="7">
         <v>10051</v>
@@ -1943,7 +1946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:29">
       <c r="B11" s="13">
         <v>1007</v>
       </c>
@@ -1951,11 +1954,11 @@
         <v>32</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>36</v>
@@ -1964,7 +1967,7 @@
         <v>10001</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J11" s="7">
         <v>10051</v>
@@ -2027,7 +2030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:29">
       <c r="B12" s="13">
         <v>1008</v>
       </c>
@@ -2035,11 +2038,11 @@
         <v>32</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>36</v>
@@ -2048,7 +2051,7 @@
         <v>10001</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J12" s="7">
         <v>10051</v>
@@ -2111,7 +2114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:29">
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
@@ -2141,7 +2144,7 @@
       <c r="AB13" s="7"/>
       <c r="AC13" s="11"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:29">
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -2171,7 +2174,7 @@
       <c r="AB14" s="7"/>
       <c r="AC14" s="11"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:29">
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
@@ -2201,7 +2204,7 @@
       <c r="AB15" s="7"/>
       <c r="AC15" s="11"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:29">
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
@@ -2231,7 +2234,7 @@
       <c r="AB16" s="7"/>
       <c r="AC16" s="11"/>
     </row>
-    <row r="17">
+    <row r="17" spans="2:29">
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
@@ -2261,7 +2264,7 @@
       <c r="AB17" s="7"/>
       <c r="AC17" s="11"/>
     </row>
-    <row r="18">
+    <row r="18" spans="2:29">
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -2291,7 +2294,7 @@
       <c r="AB18" s="7"/>
       <c r="AC18" s="11"/>
     </row>
-    <row r="19">
+    <row r="19" spans="2:29">
       <c r="H19" s="9"/>
       <c r="I19" s="10"/>
       <c r="J19" s="7"/>
@@ -2315,7 +2318,7 @@
       <c r="AB19" s="7"/>
       <c r="AC19" s="11"/>
     </row>
-    <row r="20">
+    <row r="20" spans="2:29">
       <c r="H20" s="9"/>
       <c r="I20" s="10"/>
       <c r="J20" s="7"/>
@@ -2339,7 +2342,7 @@
       <c r="AB20" s="7"/>
       <c r="AC20" s="11"/>
     </row>
-    <row r="21">
+    <row r="21" spans="2:29">
       <c r="H21" s="9"/>
       <c r="I21" s="10"/>
       <c r="J21" s="7"/>
@@ -2363,7 +2366,7 @@
       <c r="AB21" s="7"/>
       <c r="AC21" s="11"/>
     </row>
-    <row r="22">
+    <row r="22" spans="2:29">
       <c r="H22" s="9"/>
       <c r="I22" s="10"/>
       <c r="J22" s="7"/>
@@ -2387,7 +2390,7 @@
       <c r="AB22" s="7"/>
       <c r="AC22" s="11"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:29">
       <c r="H23" s="9"/>
       <c r="I23" s="10"/>
       <c r="J23" s="7"/>
@@ -2411,7 +2414,7 @@
       <c r="AB23" s="7"/>
       <c r="AC23" s="11"/>
     </row>
-    <row r="24">
+    <row r="24" spans="2:29">
       <c r="H24" s="9"/>
       <c r="I24" s="10"/>
       <c r="J24" s="7"/>
@@ -2435,7 +2438,7 @@
       <c r="AB24" s="7"/>
       <c r="AC24" s="11"/>
     </row>
-    <row r="25">
+    <row r="25" spans="2:29">
       <c r="H25" s="9"/>
       <c r="I25" s="10"/>
       <c r="J25" s="7"/>
@@ -2459,7 +2462,7 @@
       <c r="AB25" s="7"/>
       <c r="AC25" s="11"/>
     </row>
-    <row r="26">
+    <row r="26" spans="2:29">
       <c r="H26" s="9"/>
       <c r="I26" s="10"/>
       <c r="J26" s="7"/>
@@ -2483,7 +2486,7 @@
       <c r="AB26" s="7"/>
       <c r="AC26" s="11"/>
     </row>
-    <row r="27">
+    <row r="27" spans="2:29">
       <c r="H27" s="9"/>
       <c r="I27" s="10"/>
       <c r="J27" s="7"/>
@@ -2508,7 +2511,7 @@
       <c r="AC27" s="11"/>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="18">
     <mergeCell ref="H1:AK1"/>
     <mergeCell ref="H2:AK2"/>
     <mergeCell ref="H3:AK3"/>
@@ -2532,9 +2535,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
@@ -203,7 +203,7 @@
     <t>Agou_Icon</t>
   </si>
   <si>
-    <t>1500</t>
+    <t>2500</t>
   </si>
   <si>
     <t>Ayin</t>
@@ -1895,7 +1895,7 @@
         <v>10061</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N10" s="7">
         <v>10071</v>
@@ -1979,7 +1979,7 @@
         <v>10061</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N11" s="7">
         <v>10071</v>
@@ -2063,7 +2063,7 @@
         <v>10061</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N12" s="7">
         <v>10071</v>

--- a/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -197,25 +197,43 @@
     <t>战士</t>
   </si>
   <si>
-    <t>Agou</t>
-  </si>
-  <si>
-    <t>Agou_Icon</t>
-  </si>
-  <si>
-    <t>2500</t>
+    <t>Agou1</t>
+  </si>
+  <si>
+    <t>export (32)_0</t>
+  </si>
+  <si>
+    <t>3000</t>
   </si>
   <si>
     <t>Ayin</t>
   </si>
   <si>
-    <t>Ayin_Icon</t>
-  </si>
-  <si>
-    <t>Aniao</t>
-  </si>
-  <si>
-    <t>Aniao_Icon</t>
+    <t>export (32)_1</t>
+  </si>
+  <si>
+    <t>Axiong</t>
+  </si>
+  <si>
+    <t>export (32)_3</t>
+  </si>
+  <si>
+    <t>Axi</t>
+  </si>
+  <si>
+    <t>export (32)_6</t>
+  </si>
+  <si>
+    <t>Atu</t>
+  </si>
+  <si>
+    <t>export (32)_4</t>
+  </si>
+  <si>
+    <t>Aqi</t>
+  </si>
+  <si>
+    <t>export (32)_5</t>
   </si>
 </sst>
 </file>
@@ -854,7 +872,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -889,6 +907,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1210,7 +1231,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -2030,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29">
+    <row r="12" customFormat="1" spans="1:29">
       <c r="B12" s="13">
         <v>1008</v>
       </c>
@@ -2114,95 +2135,257 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29">
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
+    <row r="13" customFormat="1" spans="1:29">
+      <c r="B13" s="13">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>63</v>
+      </c>
       <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="10"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="10"/>
-      <c r="AB13" s="7"/>
-      <c r="AC13" s="11"/>
+      <c r="F13" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="9">
+        <v>10001</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="7">
+        <v>10051</v>
+      </c>
+      <c r="K13" s="10">
+        <v>500</v>
+      </c>
+      <c r="L13" s="9">
+        <v>10061</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N13" s="7">
+        <v>10071</v>
+      </c>
+      <c r="O13" s="10">
+        <v>1780</v>
+      </c>
+      <c r="P13" s="7">
+        <v>10081</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>68000</v>
+      </c>
+      <c r="R13" s="7">
+        <v>1009</v>
+      </c>
+      <c r="S13" s="11">
+        <v>0</v>
+      </c>
+      <c r="T13" s="7">
+        <v>10021</v>
+      </c>
+      <c r="U13" s="10">
+        <v>1000</v>
+      </c>
+      <c r="V13" s="7">
+        <v>1001</v>
+      </c>
+      <c r="W13" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X13" s="7">
+        <v>10041</v>
+      </c>
+      <c r="Y13" s="10">
+        <v>1000</v>
+      </c>
+      <c r="Z13" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AA13" s="10">
+        <v>1000</v>
+      </c>
+      <c r="AB13" s="7">
+        <v>1015</v>
+      </c>
+      <c r="AC13" s="11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="14" spans="1:29">
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
+    <row r="14" customFormat="1" spans="1:29">
+      <c r="B14" s="13">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>65</v>
+      </c>
       <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="10"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="11"/>
+      <c r="F14" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="9">
+        <v>10001</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="7">
+        <v>10051</v>
+      </c>
+      <c r="K14" s="10">
+        <v>500</v>
+      </c>
+      <c r="L14" s="9">
+        <v>10061</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N14" s="7">
+        <v>10071</v>
+      </c>
+      <c r="O14" s="10">
+        <v>1780</v>
+      </c>
+      <c r="P14" s="7">
+        <v>10081</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>68000</v>
+      </c>
+      <c r="R14" s="7">
+        <v>1009</v>
+      </c>
+      <c r="S14" s="11">
+        <v>0</v>
+      </c>
+      <c r="T14" s="7">
+        <v>10021</v>
+      </c>
+      <c r="U14" s="10">
+        <v>1000</v>
+      </c>
+      <c r="V14" s="7">
+        <v>1001</v>
+      </c>
+      <c r="W14" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X14" s="7">
+        <v>10041</v>
+      </c>
+      <c r="Y14" s="10">
+        <v>1000</v>
+      </c>
+      <c r="Z14" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AA14" s="10">
+        <v>1000</v>
+      </c>
+      <c r="AB14" s="7">
+        <v>1015</v>
+      </c>
+      <c r="AC14" s="11">
+        <v>1</v>
+      </c>
     </row>
-    <row r="15" spans="1:29">
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
+    <row r="15" customFormat="1" spans="1:29">
+      <c r="B15" s="13">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>67</v>
+      </c>
       <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="10"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="10"/>
-      <c r="AB15" s="7"/>
-      <c r="AC15" s="11"/>
+      <c r="F15" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="9">
+        <v>10001</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="7">
+        <v>10051</v>
+      </c>
+      <c r="K15" s="10">
+        <v>500</v>
+      </c>
+      <c r="L15" s="9">
+        <v>10061</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="N15" s="7">
+        <v>10071</v>
+      </c>
+      <c r="O15" s="10">
+        <v>1780</v>
+      </c>
+      <c r="P15" s="7">
+        <v>10081</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>68000</v>
+      </c>
+      <c r="R15" s="7">
+        <v>1009</v>
+      </c>
+      <c r="S15" s="11">
+        <v>0</v>
+      </c>
+      <c r="T15" s="7">
+        <v>10021</v>
+      </c>
+      <c r="U15" s="10">
+        <v>1000</v>
+      </c>
+      <c r="V15" s="7">
+        <v>1001</v>
+      </c>
+      <c r="W15" s="10">
+        <v>1000</v>
+      </c>
+      <c r="X15" s="7">
+        <v>10041</v>
+      </c>
+      <c r="Y15" s="10">
+        <v>1000</v>
+      </c>
+      <c r="Z15" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AA15" s="10">
+        <v>1000</v>
+      </c>
+      <c r="AB15" s="7">
+        <v>1015</v>
+      </c>
+      <c r="AC15" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:29">
       <c r="B16" s="13"/>
@@ -2234,13 +2417,8 @@
       <c r="AB16" s="7"/>
       <c r="AC16" s="11"/>
     </row>
-    <row r="17" spans="2:29">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+    <row r="17" spans="4:29">
+      <c r="D17" s="14"/>
       <c r="H17" s="9"/>
       <c r="I17" s="10"/>
       <c r="J17" s="7"/>
@@ -2264,13 +2442,8 @@
       <c r="AB17" s="7"/>
       <c r="AC17" s="11"/>
     </row>
-    <row r="18" spans="2:29">
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+    <row r="18" spans="4:29">
+      <c r="D18" s="14"/>
       <c r="H18" s="9"/>
       <c r="I18" s="10"/>
       <c r="J18" s="7"/>
@@ -2294,7 +2467,8 @@
       <c r="AB18" s="7"/>
       <c r="AC18" s="11"/>
     </row>
-    <row r="19" spans="2:29">
+    <row r="19" spans="4:29">
+      <c r="D19" s="14"/>
       <c r="H19" s="9"/>
       <c r="I19" s="10"/>
       <c r="J19" s="7"/>
@@ -2318,7 +2492,8 @@
       <c r="AB19" s="7"/>
       <c r="AC19" s="11"/>
     </row>
-    <row r="20" spans="2:29">
+    <row r="20" spans="4:29">
+      <c r="D20" s="14"/>
       <c r="H20" s="9"/>
       <c r="I20" s="10"/>
       <c r="J20" s="7"/>
@@ -2342,7 +2517,8 @@
       <c r="AB20" s="7"/>
       <c r="AC20" s="11"/>
     </row>
-    <row r="21" spans="2:29">
+    <row r="21" spans="4:29">
+      <c r="D21" s="14"/>
       <c r="H21" s="9"/>
       <c r="I21" s="10"/>
       <c r="J21" s="7"/>
@@ -2366,7 +2542,8 @@
       <c r="AB21" s="7"/>
       <c r="AC21" s="11"/>
     </row>
-    <row r="22" spans="2:29">
+    <row r="22" spans="4:29">
+      <c r="D22" s="14"/>
       <c r="H22" s="9"/>
       <c r="I22" s="10"/>
       <c r="J22" s="7"/>
@@ -2390,7 +2567,7 @@
       <c r="AB22" s="7"/>
       <c r="AC22" s="11"/>
     </row>
-    <row r="23" spans="2:29">
+    <row r="23" spans="4:29">
       <c r="H23" s="9"/>
       <c r="I23" s="10"/>
       <c r="J23" s="7"/>
@@ -2414,7 +2591,7 @@
       <c r="AB23" s="7"/>
       <c r="AC23" s="11"/>
     </row>
-    <row r="24" spans="2:29">
+    <row r="24" spans="4:29">
       <c r="H24" s="9"/>
       <c r="I24" s="10"/>
       <c r="J24" s="7"/>
@@ -2438,7 +2615,7 @@
       <c r="AB24" s="7"/>
       <c r="AC24" s="11"/>
     </row>
-    <row r="25" spans="2:29">
+    <row r="25" spans="4:29">
       <c r="H25" s="9"/>
       <c r="I25" s="10"/>
       <c r="J25" s="7"/>
@@ -2461,54 +2638,6 @@
       <c r="AA25" s="10"/>
       <c r="AB25" s="7"/>
       <c r="AC25" s="11"/>
-    </row>
-    <row r="26" spans="2:29">
-      <c r="H26" s="9"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="10"/>
-      <c r="AB26" s="7"/>
-      <c r="AC26" s="11"/>
-    </row>
-    <row r="27" spans="2:29">
-      <c r="H27" s="9"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="10"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="10"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="10"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="11"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="10"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="10"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="10"/>
-      <c r="Z27" s="7"/>
-      <c r="AA27" s="10"/>
-      <c r="AB27" s="7"/>
-      <c r="AC27" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -201,9 +201,6 @@
   </si>
   <si>
     <t>export (32)_0</t>
-  </si>
-  <si>
-    <t>3000</t>
   </si>
   <si>
     <t>Ayin</t>
@@ -1904,7 +1901,7 @@
         <v>10001</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="J10" s="7">
         <v>10051</v>
@@ -1975,11 +1972,11 @@
         <v>32</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>36</v>
@@ -1988,7 +1985,7 @@
         <v>10001</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="J11" s="7">
         <v>10051</v>
@@ -2059,11 +2056,11 @@
         <v>32</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>36</v>
@@ -2072,7 +2069,7 @@
         <v>10001</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="J12" s="7">
         <v>10051</v>
@@ -2143,11 +2140,11 @@
         <v>32</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>36</v>
@@ -2156,7 +2153,7 @@
         <v>10001</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="J13" s="7">
         <v>10051</v>
@@ -2227,11 +2224,11 @@
         <v>32</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>36</v>
@@ -2240,7 +2237,7 @@
         <v>10001</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="J14" s="7">
         <v>10051</v>
@@ -2311,11 +2308,11 @@
         <v>32</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>36</v>
@@ -2324,7 +2321,7 @@
         <v>10001</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="J15" s="7">
         <v>10051</v>

--- a/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
+++ b/Packages/cn.etetet.map/Luban/Config/Datas/Unit.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="83">
   <si>
     <t>##var</t>
   </si>
@@ -125,6 +125,9 @@
     <t>Phase</t>
   </si>
   <si>
+    <t>AttackBase</t>
+  </si>
+  <si>
     <t>Player</t>
   </si>
   <si>
@@ -231,6 +234,48 @@
   </si>
   <si>
     <t>export (32)_5</t>
+  </si>
+  <si>
+    <t>XiaoMao</t>
+  </si>
+  <si>
+    <t>近战突刺小怪</t>
+  </si>
+  <si>
+    <t>盗贼</t>
+  </si>
+  <si>
+    <t>XiaoHou</t>
+  </si>
+  <si>
+    <t>目标点延迟爆炸小怪</t>
+  </si>
+  <si>
+    <t>猎人</t>
+  </si>
+  <si>
+    <t>XiaoYing</t>
+  </si>
+  <si>
+    <t>双段回旋小怪</t>
+  </si>
+  <si>
+    <t>恶魔猎手</t>
+  </si>
+  <si>
+    <t>XiaoE</t>
+  </si>
+  <si>
+    <t>扇形压制精英</t>
+  </si>
+  <si>
+    <t>BearBoss</t>
+  </si>
+  <si>
+    <t>双技能轮转 Boss</t>
+  </si>
+  <si>
+    <t>圣骑士</t>
   </si>
 </sst>
 </file>
@@ -724,180 +769,180 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="0" applyFont="0" fillId="5" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="6" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="7" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="7" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="8" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="34" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="3" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -906,7 +951,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1226,9 +1271,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr/>
-  <dimension ref="A1:AK25"/>
+  <dimension ref="A1:AE25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
@@ -1261,8 +1306,8 @@
     <col min="37" max="37" width="2.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1306,8 +1351,8 @@
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
     </row>
-    <row r="2" spans="1:29">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="0" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1351,8 +1396,8 @@
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
     </row>
-    <row r="3" spans="1:29">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1"/>
@@ -1388,8 +1433,8 @@
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
     </row>
-    <row r="4" spans="1:29">
-      <c r="A4" t="s">
+    <row r="4">
+      <c r="A4" s="0" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -1454,31 +1499,34 @@
         <v>31</v>
       </c>
       <c r="AC4" s="6"/>
+      <c r="AD4" s="0" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="5" spans="1:29">
+    <row r="5">
       <c r="B5" s="7">
         <v>1001</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9">
         <v>10001</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J5" s="7">
         <v>10051</v>
@@ -1490,7 +1538,7 @@
         <v>10061</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N5" s="7">
         <v>10071</v>
@@ -1540,25 +1588,31 @@
       <c r="AC5" s="11">
         <v>1</v>
       </c>
+      <c r="AD5" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE5" s="0">
+        <v>100</v>
+      </c>
     </row>
-    <row r="6" spans="1:29">
+    <row r="6">
       <c r="B6" s="7">
         <v>1002</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H6" s="9">
         <v>10001</v>
@@ -1626,25 +1680,31 @@
       <c r="AC6" s="11">
         <v>1</v>
       </c>
+      <c r="AD6" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE6" s="0">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:29">
+    <row r="7">
       <c r="B7" s="7">
         <v>1003</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H7" s="9">
         <v>10001</v>
@@ -1686,13 +1746,13 @@
         <v>10021</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V7" s="7">
         <v>1001</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X7" s="7">
         <v>10041</v>
@@ -1712,25 +1772,31 @@
       <c r="AC7" s="11">
         <v>1</v>
       </c>
+      <c r="AD7" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE7" s="0">
+        <v>50</v>
+      </c>
     </row>
-    <row r="8" spans="1:29">
+    <row r="8">
       <c r="B8" s="7">
         <v>1004</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H8" s="9">
         <v>10001</v>
@@ -1798,25 +1864,31 @@
       <c r="AC8" s="11">
         <v>1</v>
       </c>
+      <c r="AD8" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE8" s="0">
+        <v>80</v>
+      </c>
     </row>
-    <row r="9" spans="1:29">
+    <row r="9">
       <c r="B9" s="7">
         <v>1005</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H9" s="9">
         <v>10001</v>
@@ -1879,29 +1951,35 @@
       <c r="AC9" s="11">
         <v>1</v>
       </c>
+      <c r="AD9" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE9" s="0">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:29">
+    <row r="10">
       <c r="B10" s="13">
         <v>1006</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H10" s="9">
         <v>10001</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J10" s="7">
         <v>10051</v>
@@ -1913,7 +1991,7 @@
         <v>10061</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N10" s="7">
         <v>10071</v>
@@ -1963,29 +2041,35 @@
       <c r="AC10" s="11">
         <v>1</v>
       </c>
+      <c r="AD10" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE10" s="0">
+        <v>100</v>
+      </c>
     </row>
-    <row r="11" spans="1:29">
+    <row r="11">
       <c r="B11" s="13">
         <v>1007</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H11" s="9">
         <v>10001</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J11" s="7">
         <v>10051</v>
@@ -1997,7 +2081,7 @@
         <v>10061</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N11" s="7">
         <v>10071</v>
@@ -2047,29 +2131,35 @@
       <c r="AC11" s="11">
         <v>1</v>
       </c>
+      <c r="AD11" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE11" s="0">
+        <v>100</v>
+      </c>
     </row>
-    <row r="12" customFormat="1" spans="1:29">
+    <row r="12">
       <c r="B12" s="13">
         <v>1008</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H12" s="9">
         <v>10001</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J12" s="7">
         <v>10051</v>
@@ -2081,7 +2171,7 @@
         <v>10061</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N12" s="7">
         <v>10071</v>
@@ -2131,29 +2221,35 @@
       <c r="AC12" s="11">
         <v>1</v>
       </c>
+      <c r="AD12" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE12" s="0">
+        <v>100</v>
+      </c>
     </row>
-    <row r="13" customFormat="1" spans="1:29">
+    <row r="13">
       <c r="B13" s="13">
         <v>1009</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H13" s="9">
         <v>10001</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J13" s="7">
         <v>10051</v>
@@ -2165,7 +2261,7 @@
         <v>10061</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N13" s="7">
         <v>10071</v>
@@ -2215,29 +2311,35 @@
       <c r="AC13" s="11">
         <v>1</v>
       </c>
+      <c r="AD13" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE13" s="0">
+        <v>100</v>
+      </c>
     </row>
-    <row r="14" customFormat="1" spans="1:29">
+    <row r="14">
       <c r="B14" s="13">
         <v>1010</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H14" s="9">
         <v>10001</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J14" s="7">
         <v>10051</v>
@@ -2249,7 +2351,7 @@
         <v>10061</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N14" s="7">
         <v>10071</v>
@@ -2299,29 +2401,35 @@
       <c r="AC14" s="11">
         <v>1</v>
       </c>
+      <c r="AD14" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE14" s="0">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" customFormat="1" spans="1:29">
+    <row r="15">
       <c r="B15" s="13">
         <v>1011</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E15" s="13"/>
       <c r="F15" s="13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H15" s="9">
         <v>10001</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J15" s="7">
         <v>10051</v>
@@ -2333,7 +2441,7 @@
         <v>10061</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N15" s="7">
         <v>10071</v>
@@ -2383,138 +2491,474 @@
       <c r="AC15" s="11">
         <v>1</v>
       </c>
+      <c r="AD15" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE15" s="0">
+        <v>100</v>
+      </c>
     </row>
-    <row r="16" spans="1:29">
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="10"/>
-      <c r="AB16" s="7"/>
-      <c r="AC16" s="11"/>
+    <row r="16">
+      <c r="B16" s="13">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="H16" s="9">
+        <v>10001</v>
+      </c>
+      <c r="I16" s="10">
+        <v>2350</v>
+      </c>
+      <c r="J16" s="7">
+        <v>10051</v>
+      </c>
+      <c r="K16" s="10">
+        <v>430</v>
+      </c>
+      <c r="L16" s="9">
+        <v>10061</v>
+      </c>
+      <c r="M16" s="10">
+        <v>10000</v>
+      </c>
+      <c r="N16" s="7">
+        <v>10071</v>
+      </c>
+      <c r="O16" s="10">
+        <v>500</v>
+      </c>
+      <c r="P16" s="7">
+        <v>10081</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>30000</v>
+      </c>
+      <c r="R16" s="7">
+        <v>1009</v>
+      </c>
+      <c r="S16" s="11">
+        <v>330101</v>
+      </c>
+      <c r="T16" s="7">
+        <v>10021</v>
+      </c>
+      <c r="U16" s="10">
+        <v>260</v>
+      </c>
+      <c r="V16" s="7">
+        <v>1001</v>
+      </c>
+      <c r="W16" s="10">
+        <v>260</v>
+      </c>
+      <c r="X16" s="7">
+        <v>10041</v>
+      </c>
+      <c r="Y16" s="10">
+        <v>100</v>
+      </c>
+      <c r="Z16" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AA16" s="10">
+        <v>100</v>
+      </c>
+      <c r="AB16" s="7">
+        <v>1015</v>
+      </c>
+      <c r="AC16" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE16" s="0">
+        <v>60</v>
+      </c>
     </row>
-    <row r="17" spans="4:29">
-      <c r="D17" s="14"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="10"/>
-      <c r="AB17" s="7"/>
-      <c r="AC17" s="11"/>
+    <row r="17">
+      <c r="B17" s="0">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="9">
+        <v>10001</v>
+      </c>
+      <c r="I17" s="10">
+        <v>2100</v>
+      </c>
+      <c r="J17" s="7">
+        <v>10051</v>
+      </c>
+      <c r="K17" s="10">
+        <v>420</v>
+      </c>
+      <c r="L17" s="9">
+        <v>10061</v>
+      </c>
+      <c r="M17" s="10">
+        <v>11000</v>
+      </c>
+      <c r="N17" s="7">
+        <v>10071</v>
+      </c>
+      <c r="O17" s="10">
+        <v>500</v>
+      </c>
+      <c r="P17" s="7">
+        <v>10081</v>
+      </c>
+      <c r="Q17" s="10">
+        <v>30000</v>
+      </c>
+      <c r="R17" s="7">
+        <v>1009</v>
+      </c>
+      <c r="S17" s="11">
+        <v>330102</v>
+      </c>
+      <c r="T17" s="7">
+        <v>10021</v>
+      </c>
+      <c r="U17" s="10">
+        <v>220</v>
+      </c>
+      <c r="V17" s="7">
+        <v>1001</v>
+      </c>
+      <c r="W17" s="10">
+        <v>220</v>
+      </c>
+      <c r="X17" s="7">
+        <v>10041</v>
+      </c>
+      <c r="Y17" s="10">
+        <v>100</v>
+      </c>
+      <c r="Z17" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AA17" s="10">
+        <v>100</v>
+      </c>
+      <c r="AB17" s="7">
+        <v>1015</v>
+      </c>
+      <c r="AC17" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE17" s="0">
+        <v>70</v>
+      </c>
     </row>
-    <row r="18" spans="4:29">
-      <c r="D18" s="14"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="11"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="7"/>
-      <c r="AC18" s="11"/>
+    <row r="18">
+      <c r="B18" s="0">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="9">
+        <v>10001</v>
+      </c>
+      <c r="I18" s="10">
+        <v>2250</v>
+      </c>
+      <c r="J18" s="7">
+        <v>10051</v>
+      </c>
+      <c r="K18" s="10">
+        <v>410</v>
+      </c>
+      <c r="L18" s="9">
+        <v>10061</v>
+      </c>
+      <c r="M18" s="10">
+        <v>12000</v>
+      </c>
+      <c r="N18" s="7">
+        <v>10071</v>
+      </c>
+      <c r="O18" s="10">
+        <v>520</v>
+      </c>
+      <c r="P18" s="7">
+        <v>10081</v>
+      </c>
+      <c r="Q18" s="10">
+        <v>30000</v>
+      </c>
+      <c r="R18" s="7">
+        <v>1009</v>
+      </c>
+      <c r="S18" s="11">
+        <v>330103</v>
+      </c>
+      <c r="T18" s="7">
+        <v>10021</v>
+      </c>
+      <c r="U18" s="10">
+        <v>210</v>
+      </c>
+      <c r="V18" s="7">
+        <v>1001</v>
+      </c>
+      <c r="W18" s="10">
+        <v>210</v>
+      </c>
+      <c r="X18" s="7">
+        <v>10041</v>
+      </c>
+      <c r="Y18" s="10">
+        <v>100</v>
+      </c>
+      <c r="Z18" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AA18" s="10">
+        <v>100</v>
+      </c>
+      <c r="AB18" s="7">
+        <v>1015</v>
+      </c>
+      <c r="AC18" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE18" s="0">
+        <v>65</v>
+      </c>
     </row>
-    <row r="19" spans="4:29">
-      <c r="D19" s="14"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="10"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="10"/>
-      <c r="AB19" s="7"/>
-      <c r="AC19" s="11"/>
+    <row r="19">
+      <c r="B19" s="0">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="9">
+        <v>10001</v>
+      </c>
+      <c r="I19" s="10">
+        <v>1750</v>
+      </c>
+      <c r="J19" s="7">
+        <v>10051</v>
+      </c>
+      <c r="K19" s="10">
+        <v>520</v>
+      </c>
+      <c r="L19" s="9">
+        <v>10061</v>
+      </c>
+      <c r="M19" s="10">
+        <v>11000</v>
+      </c>
+      <c r="N19" s="7">
+        <v>10071</v>
+      </c>
+      <c r="O19" s="10">
+        <v>620</v>
+      </c>
+      <c r="P19" s="7">
+        <v>10081</v>
+      </c>
+      <c r="Q19" s="10">
+        <v>45000</v>
+      </c>
+      <c r="R19" s="7">
+        <v>1009</v>
+      </c>
+      <c r="S19" s="11">
+        <v>330104</v>
+      </c>
+      <c r="T19" s="7">
+        <v>10021</v>
+      </c>
+      <c r="U19" s="10">
+        <v>520</v>
+      </c>
+      <c r="V19" s="7">
+        <v>1001</v>
+      </c>
+      <c r="W19" s="10">
+        <v>520</v>
+      </c>
+      <c r="X19" s="7">
+        <v>10041</v>
+      </c>
+      <c r="Y19" s="10">
+        <v>100</v>
+      </c>
+      <c r="Z19" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AA19" s="10">
+        <v>100</v>
+      </c>
+      <c r="AB19" s="7">
+        <v>1015</v>
+      </c>
+      <c r="AC19" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE19" s="0">
+        <v>150</v>
+      </c>
     </row>
-    <row r="20" spans="4:29">
-      <c r="D20" s="14"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="10"/>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="10"/>
-      <c r="AB20" s="7"/>
-      <c r="AC20" s="11"/>
+    <row r="20">
+      <c r="B20" s="0">
+        <v>1016</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="H20" s="9">
+        <v>10001</v>
+      </c>
+      <c r="I20" s="10">
+        <v>1850</v>
+      </c>
+      <c r="J20" s="7">
+        <v>10051</v>
+      </c>
+      <c r="K20" s="10">
+        <v>600</v>
+      </c>
+      <c r="L20" s="9">
+        <v>10061</v>
+      </c>
+      <c r="M20" s="10">
+        <v>12000</v>
+      </c>
+      <c r="N20" s="7">
+        <v>10071</v>
+      </c>
+      <c r="O20" s="10">
+        <v>720</v>
+      </c>
+      <c r="P20" s="7">
+        <v>10081</v>
+      </c>
+      <c r="Q20" s="10">
+        <v>60000</v>
+      </c>
+      <c r="R20" s="7">
+        <v>1009</v>
+      </c>
+      <c r="S20" s="11">
+        <v>330105</v>
+      </c>
+      <c r="T20" s="7">
+        <v>10021</v>
+      </c>
+      <c r="U20" s="10">
+        <v>960</v>
+      </c>
+      <c r="V20" s="7">
+        <v>1001</v>
+      </c>
+      <c r="W20" s="10">
+        <v>960</v>
+      </c>
+      <c r="X20" s="7">
+        <v>10041</v>
+      </c>
+      <c r="Y20" s="10">
+        <v>100</v>
+      </c>
+      <c r="Z20" s="7">
+        <v>1003</v>
+      </c>
+      <c r="AA20" s="10">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="7">
+        <v>1015</v>
+      </c>
+      <c r="AC20" s="11">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="0">
+        <v>10101</v>
+      </c>
+      <c r="AE20" s="0">
+        <v>300</v>
+      </c>
     </row>
-    <row r="21" spans="4:29">
+    <row r="21">
       <c r="D21" s="14"/>
       <c r="H21" s="9"/>
       <c r="I21" s="10"/>
@@ -2539,7 +2983,7 @@
       <c r="AB21" s="7"/>
       <c r="AC21" s="11"/>
     </row>
-    <row r="22" spans="4:29">
+    <row r="22">
       <c r="D22" s="14"/>
       <c r="H22" s="9"/>
       <c r="I22" s="10"/>
@@ -2564,7 +3008,7 @@
       <c r="AB22" s="7"/>
       <c r="AC22" s="11"/>
     </row>
-    <row r="23" spans="4:29">
+    <row r="23">
       <c r="H23" s="9"/>
       <c r="I23" s="10"/>
       <c r="J23" s="7"/>
@@ -2588,7 +3032,7 @@
       <c r="AB23" s="7"/>
       <c r="AC23" s="11"/>
     </row>
-    <row r="24" spans="4:29">
+    <row r="24">
       <c r="H24" s="9"/>
       <c r="I24" s="10"/>
       <c r="J24" s="7"/>
@@ -2612,7 +3056,7 @@
       <c r="AB24" s="7"/>
       <c r="AC24" s="11"/>
     </row>
-    <row r="25" spans="4:29">
+    <row r="25">
       <c r="H25" s="9"/>
       <c r="I25" s="10"/>
       <c r="J25" s="7"/>
@@ -2637,7 +3081,7 @@
       <c r="AC25" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells>
     <mergeCell ref="H1:AK1"/>
     <mergeCell ref="H2:AK2"/>
     <mergeCell ref="H3:AK3"/>
@@ -2661,4 +3105,9 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>